--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1996</v>
+        <v>24.7873</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7349</v>
+        <v>19.2781</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4647</v>
+        <v>5.5091</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4038</v>
+        <v>7.9966</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0294</v>
+        <v>10.4003</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3744</v>
+        <v>-2.4036</v>
       </c>
       <c r="J2" t="n">
-        <v>11.8033</v>
+        <v>10.838</v>
       </c>
       <c r="K2" t="n">
-        <v>5.474600000000001</v>
+        <v>10.4329</v>
       </c>
       <c r="L2" t="n">
-        <v>6.3287</v>
+        <v>0.4053</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.3996</v>
+        <v>-2.8414</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4453</v>
+        <v>-0.03259999999999993</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.9542</v>
+        <v>-2.8089</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.0011</v>
+        <v>4.0895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-12.2035</v>
+        <v>-3.1158</v>
       </c>
       <c r="R2" t="n">
-        <v>8.202400000000001</v>
+        <v>7.2052</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4966</v>
+        <v>6.5959</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1565</v>
+        <v>4.715400000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>3.34</v>
+        <v>1.8806</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3005000000000004</v>
+        <v>6.1052</v>
       </c>
       <c r="W2" t="n">
-        <v>4.9786</v>
+        <v>6.8406</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.6781</v>
+        <v>-0.7353000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.621799999999999</v>
+        <v>10.4549</v>
       </c>
       <c r="E3" t="n">
-        <v>6.634300000000001</v>
+        <v>11.2866</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0126</v>
+        <v>-0.8319000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5529</v>
+        <v>1.6472</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2979</v>
+        <v>0.5140999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2552000000000001</v>
+        <v>1.1327</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8305</v>
+        <v>4.6094</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7106</v>
+        <v>2.5021</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1199</v>
+        <v>2.1074</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3835</v>
+        <v>-2.9624</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0085</v>
+        <v>-1.9879</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3751</v>
+        <v>-0.9746</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2003</v>
+        <v>5.4527</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R3" t="n">
-        <v>5.4016</v>
+        <v>9.542100000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>6.7146</v>
+        <v>6.302200000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>5.3066</v>
+        <v>5.1472</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4079</v>
+        <v>1.1548</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7402</v>
+        <v>-2.9468</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6986</v>
+        <v>5.6195</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.4386</v>
+        <v>-8.5664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3124</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.834</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4783</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6239</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8628</v>
+        <v>2.4632</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2388</v>
+        <v>4.2553</v>
       </c>
       <c r="J4" t="n">
-        <v>3.748</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.628</v>
+        <v>2.4632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.12</v>
+        <v>4.2553</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.124</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7652</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3588</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2007</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0008</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9873999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08690000000000003</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9005000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.09920000000000007</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2993</v>
+        <v>5.2828</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2993</v>
+        <v>-0.03289999999999971</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5.315799999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2993</v>
+        <v>-1.002099999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4995</v>
+        <v>0.6288</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7997</v>
+        <v>-1.631</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2993</v>
+        <v>3.296899999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4995</v>
+        <v>2.4588</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7997</v>
+        <v>0.8382000000000005</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-4.299099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.8298</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-2.4693</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.1157</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-8.9579</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>12.0736</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2.5345</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-3.4268</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.8923000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.7036</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>9.0549</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.3511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7342</v>
+        <v>3.6346</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0041</v>
+        <v>3.6146</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2699</v>
+        <v>0.02009999999999978</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4017999999999999</v>
+        <v>1.7437</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8154999999999999</v>
+        <v>6.3338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4137</v>
+        <v>-4.5902</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5579999999999999</v>
+        <v>7.9439</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5579999999999999</v>
+        <v>8.005800000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.06170000000000009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1563000000000001</v>
+        <v>-6.2002</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2573</v>
+        <v>-1.6718</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4137</v>
+        <v>-4.5284</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.6473</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>13.8263</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1359</v>
+        <v>-4.2967</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3624</v>
+        <v>-4.0358</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7735000000000001</v>
+        <v>-0.2608</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5402000000000002</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>7.885400000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1998</v>
+        <v>-7.3454</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07730000000000015</v>
+        <v>3.1366</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5526999999999997</v>
+        <v>3.5846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4753999999999999</v>
+        <v>-0.4479000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.4377</v>
+        <v>2.5911</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.3963</v>
+        <v>3.5828</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9587000000000003</v>
+        <v>-0.9915999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3187999999999995</v>
+        <v>3.3842</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.7373</v>
+        <v>4.0643</v>
       </c>
       <c r="L7" t="n">
-        <v>3.418499999999999</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.1189</v>
+        <v>-0.7932</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.659</v>
+        <v>-0.4816</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4599</v>
+        <v>-0.3118000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2009</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.2015</v>
+        <v>2.5316</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0595</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.9517</v>
+        <v>0.2004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8921000000000001</v>
+        <v>0.5353</v>
       </c>
       <c r="V7" t="n">
-        <v>4.4193</v>
+        <v>-2.7216</v>
       </c>
       <c r="W7" t="n">
-        <v>5.9185</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4992</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.641</v>
+        <v>2.7433</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.0792</v>
+        <v>2.745</v>
       </c>
       <c r="F8" t="n">
-        <v>5.4382</v>
+        <v>-0.001700000000000035</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.829499999999999</v>
+        <v>1.0063</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4473</v>
+        <v>-0.5443999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3823</v>
+        <v>1.5507</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3883000000000001</v>
+        <v>0.735</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9235</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5352000000000003</v>
+        <v>0.1216</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4412</v>
+        <v>0.2714000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5237999999999998</v>
+        <v>-1.1579</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9175</v>
+        <v>1.429</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4007</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0012</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>6.4019</v>
+        <v>1.3631</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.472</v>
+        <v>1.3477</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7891</v>
+        <v>0.2623000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1.317</v>
+        <v>1.0856</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0992</v>
+        <v>2.7217</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1606000000000001</v>
+        <v>-2.7217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0006</v>
+        <v>2.1586</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9530000000000001</v>
+        <v>-2.2415</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9538</v>
+        <v>4.400099999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4112</v>
+        <v>0.7956000000000003</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1086</v>
+        <v>-0.4414999999999996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5199</v>
+        <v>1.2371</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6617999999999999</v>
+        <v>7.745900000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02</v>
+        <v>1.5685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6417999999999999</v>
+        <v>6.1774</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2506</v>
+        <v>-6.950200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1286</v>
+        <v>-2.0102</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1218</v>
+        <v>-4.9402</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6002000000000001</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-17.7209</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6002000000000001</v>
+        <v>15.3842</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3875000000000001</v>
+        <v>3.7188</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2912000000000001</v>
+        <v>0.5104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09619999999999998</v>
+        <v>3.2083</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3996</v>
+        <v>-0.01899999999999968</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>7.2232</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3996</v>
+        <v>-7.2422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1251</v>
+        <v>-0.8940999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.373899999999999</v>
+        <v>2.3618</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.499</v>
+        <v>-3.2559</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8054000000000001</v>
+        <v>-4.3722</v>
       </c>
       <c r="H10" t="n">
-        <v>4.061299999999999</v>
+        <v>-2.0956</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.866700000000001</v>
+        <v>-2.2767</v>
       </c>
       <c r="J10" t="n">
-        <v>4.594</v>
+        <v>2.0616</v>
       </c>
       <c r="K10" t="n">
-        <v>5.971</v>
+        <v>1.1372</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3769</v>
+        <v>0.9244999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.3993</v>
+        <v>-6.4337</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9096</v>
+        <v>-3.2326</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4897</v>
+        <v>-3.2011</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0006</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4016</v>
+        <v>-5.0631</v>
       </c>
       <c r="R10" t="n">
-        <v>7.4021</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3408</v>
+        <v>4.1259</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8775999999999999</v>
+        <v>3.0244</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4631</v>
+        <v>1.1015</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9795999999999998</v>
+        <v>-0.4531000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>5.0588</v>
+        <v>2.339</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.0385</v>
+        <v>-2.7921</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5306</v>
+        <v>-1.2045</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.276400000000001</v>
+        <v>-7.201899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>6.7458</v>
+        <v>5.9973</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.2849</v>
+        <v>-9.1195</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2104</v>
+        <v>-5.0471</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0746</v>
+        <v>-4.0723</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.6292</v>
+        <v>-6.1255</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8011</v>
+        <v>-4.230399999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.828</v>
+        <v>-1.8952</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3443</v>
+        <v>-2.994</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5908000000000001</v>
+        <v>-0.8166999999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7533999999999998</v>
+        <v>-2.1772</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.2015</v>
+        <v>-7.9841</v>
       </c>
       <c r="R11" t="n">
-        <v>5.201499999999999</v>
+        <v>8.9579</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09499999999999999</v>
+        <v>-0.002399999999999847</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5646</v>
+        <v>-2.7059</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6595</v>
+        <v>2.7033</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6594</v>
+        <v>6.9438</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1189</v>
+        <v>9.613799999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4596</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0982</v>
+        <v>-1.301300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9394</v>
+        <v>-7.939400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1589</v>
+        <v>6.6379</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.506</v>
+        <v>-7.428999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.5423</v>
+        <v>-3.708299999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03620000000000026</v>
+        <v>-3.7207</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8029</v>
+        <v>-2.3615</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.1265</v>
+        <v>-2.7114</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3236</v>
+        <v>0.3498000000000004</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7033</v>
+        <v>-5.067600000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4157999999999999</v>
+        <v>-0.9969999999999998</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2874</v>
+        <v>-4.0705</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2004</v>
+        <v>5.258</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2004</v>
+        <v>-5.8422</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4007</v>
+        <v>11.0999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2129</v>
+        <v>-0.6308</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0556</v>
+        <v>-1.1332</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8428</v>
+        <v>0.5025999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5796</v>
+        <v>1.5005</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1195</v>
+        <v>1.3974</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.699</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5341</v>
+        <v>-5.7644</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0841</v>
+        <v>-5.7638</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5501</v>
+        <v>-0.000800000000000356</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6671</v>
+        <v>-2.7602</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1981</v>
+        <v>-1.0544</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4689</v>
+        <v>-1.7057</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9429</v>
+        <v>0.1986000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3671</v>
+        <v>0.8624000000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.31</v>
+        <v>-0.6640000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2756999999999999</v>
+        <v>-2.9586</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5653</v>
+        <v>-1.917</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8411000000000001</v>
+        <v>-1.0418</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.401</v>
+        <v>-3.3105</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2006</v>
+        <v>4.6736</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4068</v>
+        <v>-2.2562</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3402</v>
+        <v>-2.931</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9334</v>
+        <v>0.675</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2598</v>
+        <v>-2.1111</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5999</v>
+        <v>0.2794</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8597</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>7.160400000000004</v>
+        <v>49.7523</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.098300000000001</v>
+        <v>26.4097</v>
       </c>
       <c r="F14" t="n">
-        <v>9.2583</v>
+        <v>23.34209999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.747099999999999</v>
+        <v>-2.183999999999996</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.563400000000001</v>
+        <v>11.0317</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.1839</v>
+        <v>-13.216</v>
       </c>
       <c r="J14" t="n">
-        <v>13.2968</v>
+        <v>39.04499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>6.524399999999999</v>
+        <v>27.16679999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>6.772499999999999</v>
+        <v>11.8787</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.0441</v>
+        <v>-41.22899999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.087599999999998</v>
+        <v>-16.1351</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.9562</v>
+        <v>-25.0948</v>
       </c>
       <c r="P14" t="n">
-        <v>5.0016</v>
+        <v>26.2896</v>
       </c>
       <c r="Q14" t="n">
-        <v>-41.012</v>
+        <v>-65.2366</v>
       </c>
       <c r="R14" t="n">
-        <v>46.01330000000001</v>
+        <v>91.5258</v>
       </c>
       <c r="S14" t="n">
-        <v>9.325000000000001</v>
+        <v>13.1053</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3752</v>
+        <v>-0.3725999999999994</v>
       </c>
       <c r="U14" t="n">
-        <v>11.6998</v>
+        <v>13.4785</v>
       </c>
       <c r="V14" t="n">
-        <v>0.581</v>
+        <v>12.5417</v>
       </c>
       <c r="W14" t="n">
-        <v>27.99159999999999</v>
+        <v>52.9749</v>
       </c>
       <c r="X14" t="n">
-        <v>-27.4105</v>
+        <v>-40.43320000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>24.7873</v>
+        <v>22.0975</v>
       </c>
       <c r="E2" t="n">
-        <v>19.2781</v>
+        <v>16.5113</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5091</v>
+        <v>5.5863</v>
       </c>
       <c r="G2" t="n">
         <v>7.9966</v>
@@ -610,13 +610,13 @@
         <v>7.2052</v>
       </c>
       <c r="S2" t="n">
-        <v>6.5959</v>
+        <v>3.9062</v>
       </c>
       <c r="T2" t="n">
-        <v>4.715400000000001</v>
+        <v>1.9484</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8806</v>
+        <v>1.9579</v>
       </c>
       <c r="V2" t="n">
         <v>6.1052</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>10.4549</v>
+        <v>8.334399999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>11.2866</v>
+        <v>6.9139</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8319000000000001</v>
+        <v>1.4204</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6472</v>
+        <v>1.7437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5140999999999999</v>
+        <v>6.3338</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1327</v>
+        <v>-4.5902</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6094</v>
+        <v>7.9439</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5021</v>
+        <v>8.005800000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1074</v>
+        <v>-0.06170000000000009</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9624</v>
+        <v>-6.2002</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9879</v>
+        <v>-1.6718</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9746</v>
+        <v>-4.5284</v>
       </c>
       <c r="P3" t="n">
-        <v>5.4527</v>
+        <v>5.6473</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0895</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.542100000000001</v>
+        <v>13.8263</v>
       </c>
       <c r="S3" t="n">
-        <v>6.302200000000001</v>
+        <v>0.4033000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1472</v>
+        <v>-0.7363000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1548</v>
+        <v>1.1397</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.9468</v>
+        <v>0.5402000000000002</v>
       </c>
       <c r="W3" t="n">
-        <v>5.6195</v>
+        <v>7.885400000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-8.5664</v>
+        <v>-7.3454</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6.718500000000001</v>
+        <v>7.761699999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.718500000000001</v>
+        <v>2.2079</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5.5538</v>
       </c>
       <c r="G4" t="n">
-        <v>6.718500000000001</v>
+        <v>-1.002099999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4632</v>
+        <v>0.6288</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2553</v>
+        <v>-1.631</v>
       </c>
       <c r="J4" t="n">
-        <v>6.718500000000001</v>
+        <v>3.296899999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4632</v>
+        <v>2.4588</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2553</v>
+        <v>0.8382000000000005</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-4.299099999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.8298</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.4693</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1157</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-8.9579</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>12.0736</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.05569999999999986</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1.1858</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.1303</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.7036</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>9.0549</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-3.3511</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2828</v>
+        <v>6.765400000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03289999999999971</v>
+        <v>7.248</v>
       </c>
       <c r="F5" t="n">
-        <v>5.315799999999999</v>
+        <v>-0.4824999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.002099999999999</v>
+        <v>1.6472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6288</v>
+        <v>0.5140999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.631</v>
+        <v>1.1327</v>
       </c>
       <c r="J5" t="n">
-        <v>3.296899999999999</v>
+        <v>4.6094</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4588</v>
+        <v>2.5021</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8382000000000005</v>
+        <v>2.1074</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.299099999999999</v>
+        <v>-2.9624</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8298</v>
+        <v>-1.9879</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4693</v>
+        <v>-0.9746</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1157</v>
+        <v>5.4527</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.9579</v>
+        <v>-4.0895</v>
       </c>
       <c r="R5" t="n">
-        <v>12.0736</v>
+        <v>9.542100000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5345</v>
+        <v>2.6125</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.4268</v>
+        <v>1.1086</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8923000000000001</v>
+        <v>1.5039</v>
       </c>
       <c r="V5" t="n">
-        <v>5.7036</v>
+        <v>-2.9468</v>
       </c>
       <c r="W5" t="n">
-        <v>9.0549</v>
+        <v>5.6195</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.3511</v>
+        <v>-8.5664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6346</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6146</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02009999999999978</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7437</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>6.3338</v>
+        <v>2.4632</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.5902</v>
+        <v>4.2553</v>
       </c>
       <c r="J6" t="n">
-        <v>7.9439</v>
+        <v>6.718500000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>8.005800000000001</v>
+        <v>2.4632</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06170000000000009</v>
+        <v>4.2553</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.2002</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6718</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.5284</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.6473</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.178900000000001</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>13.8263</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.2967</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.0358</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2608</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5402000000000002</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>7.885400000000001</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.3454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1366</v>
+        <v>3.1984</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5846</v>
+        <v>3.6464</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4479000000000001</v>
+        <v>-0.4480999999999998</v>
       </c>
       <c r="G7" t="n">
         <v>2.5911</v>
@@ -1000,13 +1000,13 @@
         <v>2.5316</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7972999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2004</v>
+        <v>0.2621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5353</v>
+        <v>0.5352</v>
       </c>
       <c r="V7" t="n">
         <v>-2.7216</v>
@@ -1033,13 +1033,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7433</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2.745</v>
+        <v>2.446</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001700000000000035</v>
+        <v>0.05400000000000027</v>
       </c>
       <c r="G8" t="n">
         <v>1.0063</v>
@@ -1078,13 +1078,13 @@
         <v>1.3631</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3477</v>
+        <v>1.1043</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2623000000000001</v>
+        <v>-0.03679999999999997</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0856</v>
+        <v>1.1412</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1586</v>
+        <v>1.4935</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2415</v>
+        <v>-4.1637</v>
       </c>
       <c r="F9" t="n">
-        <v>4.400099999999999</v>
+        <v>5.6571</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7956000000000003</v>
+        <v>-9.1195</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4414999999999996</v>
+        <v>-5.0471</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2371</v>
+        <v>-4.0723</v>
       </c>
       <c r="J9" t="n">
-        <v>7.745900000000001</v>
+        <v>-6.1255</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5685</v>
+        <v>-4.230399999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1774</v>
+        <v>-1.8952</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.950200000000001</v>
+        <v>-2.994</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0102</v>
+        <v>-0.8166999999999998</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.9402</v>
+        <v>-2.1772</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3368</v>
+        <v>0.9737</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.7209</v>
+        <v>-7.9841</v>
       </c>
       <c r="R9" t="n">
-        <v>15.3842</v>
+        <v>8.9579</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7188</v>
+        <v>2.6955</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5104</v>
+        <v>0.3323</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2083</v>
+        <v>2.3632</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01899999999999968</v>
+        <v>6.9438</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2232</v>
+        <v>9.613799999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.2422</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8940999999999999</v>
+        <v>1.354</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3618</v>
+        <v>-2.0318</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2559</v>
+        <v>3.3859</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3722</v>
+        <v>0.7956000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0956</v>
+        <v>-0.4414999999999996</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2767</v>
+        <v>1.2371</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0616</v>
+        <v>7.745900000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1372</v>
+        <v>1.5685</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9244999999999999</v>
+        <v>6.1774</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.4337</v>
+        <v>-6.950200000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.2326</v>
+        <v>-2.0102</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2011</v>
+        <v>-4.9402</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1948</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0631</v>
+        <v>-17.7209</v>
       </c>
       <c r="R10" t="n">
-        <v>4.868300000000001</v>
+        <v>15.3842</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1259</v>
+        <v>2.9142</v>
       </c>
       <c r="T10" t="n">
-        <v>3.0244</v>
+        <v>0.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1015</v>
+        <v>2.194</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4531000000000001</v>
+        <v>-0.01899999999999968</v>
       </c>
       <c r="W10" t="n">
-        <v>2.339</v>
+        <v>7.2232</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7921</v>
+        <v>-7.2422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2045</v>
+        <v>-1.219500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.201899999999999</v>
+        <v>-8.2902</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9973</v>
+        <v>7.0709</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.1195</v>
+        <v>-7.428999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.0471</v>
+        <v>-3.708299999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0723</v>
+        <v>-3.7207</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.1255</v>
+        <v>-2.3615</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.230399999999999</v>
+        <v>-2.7114</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8952</v>
+        <v>0.3498000000000004</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.994</v>
+        <v>-5.067600000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8166999999999998</v>
+        <v>-0.9969999999999998</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1772</v>
+        <v>-4.0705</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9737</v>
+        <v>5.258</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9841</v>
+        <v>-5.8422</v>
       </c>
       <c r="R11" t="n">
-        <v>8.9579</v>
+        <v>11.0999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002399999999999847</v>
+        <v>-0.5487000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.7059</v>
+        <v>-1.4841</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7033</v>
+        <v>0.9352</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9438</v>
+        <v>1.5005</v>
       </c>
       <c r="W11" t="n">
-        <v>9.613799999999999</v>
+        <v>1.3974</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.67</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.301300000000001</v>
+        <v>-2.003400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.939400000000001</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.6379</v>
+        <v>-2.9562</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.428999999999999</v>
+        <v>-4.3722</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.708299999999999</v>
+        <v>-2.0956</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7207</v>
+        <v>-2.2767</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3615</v>
+        <v>2.0616</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7114</v>
+        <v>1.1372</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3498000000000004</v>
+        <v>0.9244999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.067600000000001</v>
+        <v>-6.4337</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9969999999999998</v>
+        <v>-3.2326</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.0705</v>
+        <v>-3.2011</v>
       </c>
       <c r="P12" t="n">
-        <v>5.258</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8422</v>
+        <v>-5.0631</v>
       </c>
       <c r="R12" t="n">
-        <v>11.0999</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6308</v>
+        <v>3.0166</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1332</v>
+        <v>1.6152</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5025999999999999</v>
+        <v>1.4014</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5005</v>
+        <v>-0.4531000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3974</v>
+        <v>2.339</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1031</v>
+        <v>-2.7921</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7644</v>
+        <v>-3.0908</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7638</v>
+        <v>-3.5845</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.000800000000000356</v>
+        <v>0.4939</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7602</v>
@@ -1468,13 +1468,13 @@
         <v>4.6736</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2562</v>
+        <v>0.4174</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.931</v>
+        <v>-0.7521</v>
       </c>
       <c r="U13" t="n">
-        <v>0.675</v>
+        <v>1.1695</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1111</v>
@@ -1501,16 +1501,16 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>49.7523</v>
+        <v>53.90969999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>26.4097</v>
+        <v>28.5743</v>
       </c>
       <c r="F14" t="n">
-        <v>23.34209999999999</v>
+        <v>25.3355</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.183999999999996</v>
+        <v>-2.184</v>
       </c>
       <c r="H14" t="n">
         <v>11.0317</v>
@@ -1522,7 +1522,7 @@
         <v>39.04499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>27.16679999999999</v>
+        <v>27.1668</v>
       </c>
       <c r="L14" t="n">
         <v>11.8787</v>
@@ -1543,16 +1543,16 @@
         <v>-65.2366</v>
       </c>
       <c r="R14" t="n">
-        <v>91.5258</v>
+        <v>91.52580000000003</v>
       </c>
       <c r="S14" t="n">
-        <v>13.1053</v>
+        <v>17.2629</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3725999999999994</v>
+        <v>1.7915</v>
       </c>
       <c r="U14" t="n">
-        <v>13.4785</v>
+        <v>15.4715</v>
       </c>
       <c r="V14" t="n">
         <v>12.5417</v>
